--- a/manage/export/orders.xlsx.xlsx
+++ b/manage/export/orders.xlsx.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:46</t>
+          <t>2026-10-07 17:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:46</t>
+          <t>2026-10-07 17:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:46</t>
+          <t>2026-10-07 17:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/manage/export/orders.xlsx.xlsx
+++ b/manage/export/orders.xlsx.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:53</t>
+          <t>2026-10-07 17:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:53</t>
+          <t>2026-10-07 17:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:53</t>
+          <t>2026-10-07 17:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
